--- a/artfynd/Tosktjärnberget artfynd.xlsx
+++ b/artfynd/Tosktjärnberget artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7242658</v>
+        <v>7215139</v>
       </c>
       <c r="B2" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,19 +773,597 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Ulf Hallin, Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129239902</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89292</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>510</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>682364</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7092183</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128471181</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>682547</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7092122</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128469259</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>682222</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7091995</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128469757</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>682385</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092115</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128471580</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>682467</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7092227</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128499442</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>683039</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7092240</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
